--- a/Assets/Data/Helps.xlsx
+++ b/Assets/Data/Helps.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Help" sheetId="3" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="67">
   <si>
     <t>Id</t>
   </si>
@@ -35,13 +35,13 @@
     <t>""</t>
   </si>
   <si>
-    <t>Tactics</t>
-  </si>
-  <si>
-    <t>Symbol</t>
-  </si>
-  <si>
-    <t>BattleBonus</t>
+    <t>MainMenu</t>
+  </si>
+  <si>
+    <t>MainCommand</t>
+  </si>
+  <si>
+    <t>Interrude</t>
   </si>
   <si>
     <t>Battle</t>
@@ -59,7 +59,28 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Parameter</t>
+    <t>Status1</t>
+  </si>
+  <si>
+    <t>Status2</t>
+  </si>
+  <si>
+    <t>Status3</t>
+  </si>
+  <si>
+    <t>Dungeon</t>
+  </si>
+  <si>
+    <t>Dungeon1</t>
+  </si>
+  <si>
+    <t>Dungeon2</t>
+  </si>
+  <si>
+    <t>Dungeon3</t>
+  </si>
+  <si>
+    <t>Dungeon4</t>
   </si>
   <si>
     <t>LevelUp</t>
@@ -83,81 +104,44 @@
     <t>ゲームの流れ</t>
   </si>
   <si>
+    <t>ゲームの目的</t>
+  </si>
+  <si>
     <t>◇ゲームの目的
-Normは全6層からなるステージをクリアすることが目的です。
-マスを選択してステージを進め、各階層にいるボスを討伐することで次の階層に進めます。
-◇マスの種類
-■魔物殲滅
-メンバーを選んで敵とバトルを行います。
-勝利するとバトルに参加したメンバーのLvが1上がります。
-敗北した場合でもペナルティはなくバトル前の状態に戻ります。
-■使途殲滅
-各階層のボスとバトルを行います。
-基本的に魔物殲滅と変わりません。
-■魔法選択
-候補の中から魔法を1つだけ選択して入手できます。
-入手した魔法は(Nu)を消費してメンバーに習得させることができます。
-■ショップ
-候補の中から魔法を(Nu)を消費して入手できます。
-(Nu)を消費しますが選択できる魔法の数に限りはありません。
-■仲間加入
-候補の中から仲間を1名だけ選択して加入できます。
-■仲間召喚
-未加入の仲間を1名だけ選択して加入できます。
-■トレジャー
-(Nu)を獲得します。
-◇バトル評価について
-■バトル評価
-バトルで勝利するとバトル評価を入手します。
-バトル評価の累積値の分だけバトルで勝利時に獲得する(Nu)にボーナス補正が入ります。
-■(Nu)
-Lvアップや魔法習得に必要なリソースです。
-バトルで勝利したりトレジャーマスを選んだ時に入手できます。</t>
-  </si>
-  <si>
-    <t>ゲームの目的</t>
-  </si>
-  <si>
-    <t>◇ゲームの目的
-Normは全6層からなるステージをクリアすることが目的です。
-マスを選択してステージを進め、各階層にいるボスを討伐することで次の階層に進めます。</t>
-  </si>
-  <si>
-    <t>ステージのマス</t>
-  </si>
-  <si>
-    <t>◇マスの種類
-■魔物殲滅
-メンバーを選んで敵とバトルを行います。
-勝利するとバトルに参加したメンバーのLvが1上がります。
-敗北した場合でもペナルティはなくバトル前の状態に戻ります。
-■使途殲滅
-各階層のボスとバトルを行います。
-基本的に魔物殲滅と変わりません。
-■魔法選択
-候補の中から魔法を1つだけ選択して入手できます。
-入手した魔法は(Nu)を消費してメンバーに習得させることができます。
-■ショップ
-候補の中から魔法を(Nu)を消費して入手できます。
-(Nu)を消費しますが選択できる魔法の数に限りはありません。
-■仲間加入
-候補の中から仲間を1名選択して加入します。
-■仲間召喚
-未加入の仲間を1名選択して加入します。
-■トレジャー
-(Nu)を獲得します。</t>
-  </si>
-  <si>
-    <t>バトル評価</t>
-  </si>
-  <si>
-    <t>◇バトル評価について
-■バトル評価
-バトルで勝利するとバトル評価を入手します。
-バトル評価の累積値の分だけバトルで勝利時に獲得する(Nu)にボーナス補正が入ります。
-■(Nu)
-Lvアップや魔法習得に必要なリソースです。
-バトルで勝利したりトレジャーマスを選んだ時に入手できます。</t>
+来るべき終末に向けて強い軍勢を作りましょう。
+メインメニューでは「招聘」で仲間を増やしたり「取引」でアイテムを入手するなど
+味方を強化することができます。</t>
+  </si>
+  <si>
+    <t>メインメニューコマンド</t>
+  </si>
+  <si>
+    <t>◇コマンド説明
+出撃　-　不死者のいるダンジョンに出撃します。ピリオドが1つ進みます。
+編成　-　出撃する仲間と隊列を編成します。
+報告　-　課題を確認します。課題は達成と同時に報酬が入手できます。
+　　　　 全ての重要課題を達成すると新たな課題が課せられます。
+招聘　-　仲間になるエインフェリアを加入します。
+　　　　 課題達成により招聘できる回数が増えます。
+献上　-　ダンジョンや課題達成で入手したアイテムを献上し装具やNuを入手します。
+転送　-　Nuを使用しエインフェリアの勇者適正値を調整します。
+　　　　 チャプター4以降に解放されます。
+取引　-　Nuを使用しアイテムや装具を入手します。</t>
+  </si>
+  <si>
+    <t>評価値</t>
+  </si>
+  <si>
+    <t>◇チャプターとピリオド
+・経過報告
+ピリオドが一定に達するとチャプターは終了しヘイムダルから評価を受けます。
+評価によりNuやアイテムを入手します。
+・評価値
+ダンジョン内でバトルで勝利すると評価値が増減します。
+評価値は経過報告の際にNuに変換されます。
+・(Nu)
+取引コマンドで商品購入に必要なリソースです。
+課題の達成や経過報告の際に入手できます。</t>
   </si>
   <si>
     <t>バトル</t>
@@ -274,68 +258,84 @@
 条件を設定した時は条件に一致する場合にのみ効果を発動します。</t>
   </si>
   <si>
-    <t>パラメータ</t>
-  </si>
-  <si>
-    <t>◇キャラのパラメータ
-■Lv
-Lvはバトル勝利時、または(Nu)を使用してアップします。
-Lvに応じて魔法を習得することができます。
-■パラメータ
+    <t>◇キャラクターのステータスについて
+・パラメータ
 HP：0になると戦闘不能になります。
 ATK：攻撃時のダメージ量に影響します。
 DEF：攻撃を受ける際のダメージ量に影響します。
 SPD：バトルの行動順に影響します。
-■属性適正値
+・属性適正値
 キャラ毎に5つの属性適正値があります。
-属性適正値は魔法習得する際の(Nu)使用量に影響します。
-■習得コスト
-属性適正値に応じて魔法習得する際の(Nu)使用量が変化します。
-また魔法のRankがRの場合は(Nu)使用量が2倍になります。</t>
+属性適正値は装具の特技の習得スピードに影響します。</t>
   </si>
   <si>
     <t>魔法</t>
   </si>
   <si>
     <t>◇魔法について
-■種別
-魔法にはそれぞれ種別があります。
+■種別　-　魔法にはそれぞれ種別があります。
 ・Active
-バトルでターンがまわってきた際に使用します。
-基本的に同じターン内で発動する魔法の起点になります。
+バトルで行動順がまわってきた際に使用できます。
 ・Passive
-(条件)を満たしたとき自動で発動します。
-・Messiah
-Passiveと同じく(条件)を満たしたとき自動で発動しさらに覚醒状態になります。
-バトル中1回だけ発動します。
+バトル中に(条件)を満たしたとき自動で発動します。
+・Unique
+Passiveと同じく(条件)を満たしたとき自動でバトル中1回だけ発動します。
+また覚醒状態になりステータスが大幅にアップします。
 ・Awaken
-Activeと同じくバトルでターンがまわってきた際に使用します。
+Activeと同じくバトルで行動順がまわってきた際に使用できます。
 覚醒状態の場合にのみバトル中1回だけ発動できます。
-・Enhance
-習得している魔法の効果を強化します。
-効果は作戦に設定しなくても自動で発動します。
-・Relic
-編成しているキャラクター全体に自動で効果が発動します。
-■Range
-魔法にはそれぞれ攻撃範囲があります。
-Range.Sの魔法はBackに配置した敵を対象にできません。
-ただしFrontに配置した敵がいない場合は使用できます。
-Range.Lの魔法は配置にかかわらず対象にできます。
-■CT
-一部の魔法にはCT(カウントターン)があります。
-CTは魔法を使用した後、再度使用できるまでの猶予ターンです。</t>
-  </si>
-  <si>
-    <t>作戦設定</t>
-  </si>
-  <si>
-    <t>■作戦設定
-キャラクター毎にバトル中の行動を設定します。
-作戦は魔法毎に優先順位と2つまで条件を設定できます。
-キャラクターは優先順位の高い方から使用可能になった魔法を選択します。
-Acitve・Awaken魔法は作戦に設定しなければ使用しません。
-Passive・Unique魔法は作戦に設定しなくても発動しますが
-条件を設定した時は条件に一致する場合にのみ効果を発動します。</t>
+■Range　-　攻撃範囲がRange.SとRange.Lの2種類あります。
+Range.Sの魔法は前列を飛び越えて対象を選択することができません。
+■CT　-　魔法によってCT(カウントターン)が設定されます。
+CTは行動順がまわると1つ減少し0になると再度使用できます。</t>
+  </si>
+  <si>
+    <t>装具</t>
+  </si>
+  <si>
+    <t>◇装具について
+■装具　-　キャラクターに装具を設定できます。
+装具にはステータスアップ効果や魔法を習得する効果があります。
+装具の効果は設定するだけで発揮します。
+■魔法習得　-　装具の魔法効果は一定数バトルに勝利すると会得することができます。
+会得した魔法効果は装具を外してもキャラクターに付与され続けます。
+習得するスピードはキャラクターの属性適正値によって増減します。</t>
+  </si>
+  <si>
+    <t>ダンジョン</t>
+  </si>
+  <si>
+    <t>ダンジョン探索の目的</t>
+  </si>
+  <si>
+    <t>◇ダンジョン探索の目的
+ダンジョンはボスを撃破することが目的です。
+探索中は不死者とのバトルや宝箱からアイテムが入手できます。</t>
+  </si>
+  <si>
+    <t>ダンジョンイベント</t>
+  </si>
+  <si>
+    <t>◇ダンジョンイベント
+ダンジョンには特定のオブジェクトが配置されています。
+オブジェクトに接触すると様々なイベントが発生します。</t>
+  </si>
+  <si>
+    <t>TIP1</t>
+  </si>
+  <si>
+    <t>◇進め方のコツ
+・Hpの回復手段がアイテム使用に限られているため無理に進まずに帰還しましょう。
+・こまめなセーブは忘れずに心掛けましょう。</t>
+  </si>
+  <si>
+    <t>TIP2</t>
+  </si>
+  <si>
+    <t>◇アーティファクトの注意点
+ダンジョン探索中に特殊な効力を持ったアーティファクトを入手できることがあります。
+入手時、また所有しながら未クリアのダンジョンで移動すると評価値が減少します。
+アーティファクトは献上して手放すことができます。</t>
   </si>
   <si>
     <t>レベルアップ</t>
@@ -373,10 +373,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -384,57 +384,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -462,7 +411,75 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -476,24 +493,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -515,21 +524,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -540,187 +540,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,30 +731,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -794,16 +770,34 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -823,11 +817,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -839,7 +839,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -848,136 +848,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -997,12 +997,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1307,7 +1307,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="15.6363636363636" customWidth="1"/>
@@ -1509,7 +1509,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>3000</v>
@@ -1526,7 +1526,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13">
         <v>3000</v>
@@ -1537,86 +1537,171 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>10120</v>
+        <v>4000</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
       </c>
       <c r="D14">
-        <v>1020</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>1020</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>10130</v>
+        <v>4010</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D15">
-        <v>1030</v>
+        <v>4000</v>
       </c>
       <c r="E15">
-        <v>1030</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>10140</v>
+        <v>4020</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D16">
-        <v>1040</v>
+        <v>4000</v>
       </c>
       <c r="E16">
-        <v>1040</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>10150</v>
+        <v>4030</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D17">
-        <v>1050</v>
+        <v>4000</v>
       </c>
       <c r="E17">
-        <v>1050</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
+        <v>4040</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18">
+        <v>4000</v>
+      </c>
+      <c r="E18">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>10120</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <v>1020</v>
+      </c>
+      <c r="E19">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>10130</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>1030</v>
+      </c>
+      <c r="E20">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>10140</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <v>1040</v>
+      </c>
+      <c r="E21">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>10150</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22">
+        <v>1050</v>
+      </c>
+      <c r="E22">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
         <v>10160</v>
       </c>
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
         <v>5</v>
       </c>
-      <c r="D18">
+      <c r="D23">
         <v>1060</v>
       </c>
-      <c r="E18">
+      <c r="E23">
         <v>1060</v>
       </c>
     </row>
@@ -1629,10 +1714,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
+    <col min="2" max="2" width="16.6090909090909" customWidth="1"/>
     <col min="3" max="3" width="62.8181818181818" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1641,54 +1726,52 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="409.5" spans="1:3">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1000</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" ht="52" spans="1:3">
+        <v>28</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" ht="65" spans="1:3">
       <c r="A3">
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" ht="338" spans="1:3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" ht="156" spans="1:3">
       <c r="A4">
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" ht="117" spans="1:3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" ht="143" spans="1:3">
       <c r="A5">
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" ht="299" spans="1:3">
@@ -1696,10 +1779,10 @@
         <v>2000</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" ht="65" spans="1:3">
@@ -1707,10 +1790,10 @@
         <v>2010</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" ht="65" spans="1:3">
@@ -1718,10 +1801,10 @@
         <v>2020</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" ht="143" spans="1:3">
@@ -1729,10 +1812,10 @@
         <v>2030</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="409.5" spans="1:3">
@@ -1740,32 +1823,32 @@
         <v>3000</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" ht="234" spans="1:3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" ht="130" spans="1:3">
       <c r="A11">
         <v>3010</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" ht="409.5" spans="1:3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" ht="234" spans="1:3">
       <c r="A12">
         <v>3020</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" ht="117" spans="1:3">
@@ -1773,64 +1856,117 @@
         <v>3030</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" ht="39" spans="1:3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14">
-        <v>10120</v>
+        <v>4000</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>46</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C14" s="1"/>
     </row>
     <row r="15" ht="39" spans="1:3">
       <c r="A15">
-        <v>10130</v>
+        <v>4010</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" ht="39" spans="1:3">
       <c r="A16">
+        <v>4020</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" ht="52" spans="1:3">
+      <c r="A17">
+        <v>4030</v>
+      </c>
+      <c r="B17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" ht="78" spans="1:3">
+      <c r="A18">
+        <v>4040</v>
+      </c>
+      <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" ht="39" spans="1:3">
+      <c r="A19">
+        <v>10120</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" ht="39" spans="1:3">
+      <c r="A20">
+        <v>10130</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" ht="39" spans="1:3">
+      <c r="A21">
         <v>10140</v>
       </c>
-      <c r="B16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17">
+      <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
         <v>10150</v>
       </c>
-      <c r="B17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18">
+    <row r="23" spans="1:3">
+      <c r="A23">
         <v>10160</v>
       </c>
-      <c r="B18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Assets/Data/Helps.xlsx
+++ b/Assets/Data/Helps.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Help" sheetId="3" r:id="rId1"/>
@@ -373,10 +373,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -387,26 +387,50 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -424,21 +448,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -446,19 +456,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -477,42 +501,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -525,11 +517,19 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -540,13 +540,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,7 +654,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -570,157 +720,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,41 +731,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -787,8 +752,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -798,6 +763,32 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -831,6 +822,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -839,145 +839,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1310,6 +1310,7 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
+    <col min="2" max="2" width="10.9909090909091" customWidth="1"/>
     <col min="3" max="3" width="15.6363636363636" customWidth="1"/>
     <col min="4" max="4" width="14.5454545454545" customWidth="1"/>
   </cols>

--- a/Assets/Data/Helps.xlsx
+++ b/Assets/Data/Helps.xlsx
@@ -374,8 +374,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -384,127 +384,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -530,6 +409,127 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -546,25 +546,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -576,61 +696,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -642,85 +720,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -735,16 +735,40 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -768,16 +792,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -807,30 +831,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -839,145 +839,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1669,7 +1669,7 @@
         <v>1040</v>
       </c>
       <c r="E21">
-        <v>1040</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1686,7 +1686,7 @@
         <v>1050</v>
       </c>
       <c r="E22">
-        <v>1050</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1703,7 +1703,7 @@
         <v>1060</v>
       </c>
       <c r="E23">
-        <v>1060</v>
+        <v>1030</v>
       </c>
     </row>
   </sheetData>
